--- a/3DAG and 2D Tree/Data Summaries/Spatial 1 - 10,000.xlsx
+++ b/3DAG and 2D Tree/Data Summaries/Spatial 1 - 10,000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvinc\Desktop\College\Internship\Github\Multi-Dimensional-Data-Structure\3DAG and 2D Tree\Data Summaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAADD198-9D59-4CEB-8CCC-EBB51174FFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB09903D-8343-4169-923E-888FF51533CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{1D854C81-AC11-4974-9C75-1D9353F1DFE7}"/>
   </bookViews>
@@ -2769,28 +2769,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-2478.2819</c:v>
+                  <c:v>1.3577999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3149.8189000000002</c:v>
+                  <c:v>1.2659</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-3637.4418000000001</c:v>
+                  <c:v>1.1842999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-3981.4915000000001</c:v>
+                  <c:v>1.1133</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-4347.3503000000001</c:v>
+                  <c:v>1.0456000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-4503.6704</c:v>
+                  <c:v>0.9577</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-4573.1917999999996</c:v>
+                  <c:v>0.85919999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-4694.0680000000002</c:v>
+                  <c:v>0.82340000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16180,7 +16180,7 @@
         <v>8.9912796900000007</v>
       </c>
       <c r="D137" s="1">
-        <v>-2478.2819</v>
+        <v>1.3577999999999999</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.45">
@@ -16191,7 +16191,7 @@
         <v>5.6763876700000004</v>
       </c>
       <c r="D138" s="1">
-        <v>-3149.8189000000002</v>
+        <v>1.2659</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.45">
@@ -16202,7 +16202,7 @@
         <v>4.9838734499999999</v>
       </c>
       <c r="D139" s="1">
-        <v>-3637.4418000000001</v>
+        <v>1.1842999999999999</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.45">
@@ -16213,7 +16213,7 @@
         <v>4.57352413</v>
       </c>
       <c r="D140" s="1">
-        <v>-3981.4915000000001</v>
+        <v>1.1133</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.45">
@@ -16224,7 +16224,7 @@
         <v>4.4584325099999997</v>
       </c>
       <c r="D141" s="1">
-        <v>-4347.3503000000001</v>
+        <v>1.0456000000000001</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.45">
@@ -16235,7 +16235,7 @@
         <v>4.2218049000000004</v>
       </c>
       <c r="D142" s="1">
-        <v>-4503.6704</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.45">
@@ -16246,7 +16246,7 @@
         <v>3.5612353699999999</v>
       </c>
       <c r="D143" s="1">
-        <v>-4573.1917999999996</v>
+        <v>0.85919999999999996</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.45">
@@ -16257,7 +16257,7 @@
         <v>3.41353229</v>
       </c>
       <c r="D144" s="1">
-        <v>-4694.0680000000002</v>
+        <v>0.82340000000000002</v>
       </c>
     </row>
     <row r="152" spans="4:15" x14ac:dyDescent="0.45">
